--- a/InputFiles/ICDC/TC45_ICDC_COTC021_Breed-SaintBernard.xlsx
+++ b/InputFiles/ICDC/TC45_ICDC_COTC021_Breed-SaintBernard.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10222"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10830"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/epishinavv/git/Commons_Automation/InputFiles/ICDC/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{08CEF7DF-2C5E-0C4B-A166-473806D6229C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{181BFCEB-5C4A-D549-9636-F3396F875AF1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="30240" yWindow="600" windowWidth="29040" windowHeight="15720" xr2:uid="{8362173B-D28C-47E7-8626-98E16101E601}"/>
+    <workbookView xWindow="4260" yWindow="3100" windowWidth="29040" windowHeight="15720" xr2:uid="{8362173B-D28C-47E7-8626-98E16101E601}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -128,7 +128,7 @@
 JOIN 
     df_enrollment enr ON enr."case.case_record_id" = c.case_record_id
 JOIN 
-    df_sample smp ON smp."case.case_record_id" = c.case_record_id
+    df_sample smp ON smp."case.case_id" = c.case_record_id
 LEFT JOIN 
     df_case_file cf ON cf."sample.sample_id" = smp.sample_id
 LEFT JOIN 
@@ -153,7 +153,7 @@
 FROM 
     df_sample smp
 JOIN 
-    df_case c ON smp."case.case_record_id" = c.case_record_id
+    df_case c ON smp."case.case_id" = c.case_record_id
 JOIN 
     df_publication pub ON pub."study.clinical_study_designation" = st.clinical_study_designation
 JOIN 
@@ -229,7 +229,7 @@
 JOIN 
     df_sample smp ON cf."sample.sample_id" = smp.sample_id
 JOIN 
-    df_case c ON smp."case.case_record_id" = c.case_record_id
+    df_case c ON smp."case.case_id" = c.case_record_id
 JOIN 
     df_study st ON c."study.clinical_study_designation" = st.clinical_study_designation
 JOIN 
@@ -262,6 +262,7 @@
         WHEN cf.file_name LIKE '%.fastq.gz' THEN 'fastq'
         WHEN cf.file_name LIKE '%.vcf.gz' THEN 'vcf'
         WHEN cf.file_name LIKE '%.tsv.gz' THEN 'tsv'
+        WHEN cf.file_name LIKE '%.txt.gz' THEN 'txt'
         WHEN cf.file_name LIKE '%.pdf' THEN 'pdf'
         WHEN cf.file_name LIKE '%.rtf' THEN 'rtf'
         WHEN cf.file_name LIKE '%.tbi' THEN 'tbi'
@@ -311,7 +312,7 @@
 JOIN 
     df_sample smp ON cf."sample.sample_id" = smp.sample_id
 JOIN 
-    df_case c ON smp."case.case_record_id" = c.case_record_id
+    df_case c ON smp."case.case_id" = c.case_record_id
 JOIN 
     df_study st ON c."study.clinical_study_designation" = st.clinical_study_designation
 JOIN 
